--- a/苏老师22年计划表.xlsx
+++ b/苏老师22年计划表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Desktop/workspace/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kayla/Desktop/Workspace/kayla00822.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C37DB7-7AA1-9542-9172-A2BCE149AD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F778C63E-A33D-564F-9170-E4AB6772582A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="计划表" sheetId="1" r:id="rId1"/>
@@ -456,29 +456,29 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -775,26 +775,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="1" customFormat="1" ht="45" customHeight="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
     </row>
     <row r="2" spans="1:19" s="2" customFormat="1" ht="53" customHeight="1">
       <c r="A2" s="9" t="s">
@@ -853,13 +853,13 @@
       </c>
     </row>
     <row r="3" spans="1:19" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="A3" s="31">
+      <c r="A3" s="32">
         <v>1</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="32" t="s">
         <v>20</v>
       </c>
       <c r="D3" s="13" t="s">
@@ -891,9 +891,9 @@
       </c>
     </row>
     <row r="4" spans="1:19" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
       <c r="D4" s="13" t="s">
         <v>24</v>
       </c>
@@ -918,9 +918,9 @@
       <c r="R4" s="17"/>
     </row>
     <row r="5" spans="1:19" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
       <c r="D5" s="13" t="s">
         <v>26</v>
       </c>
@@ -945,9 +945,9 @@
       <c r="R5" s="17"/>
     </row>
     <row r="6" spans="1:19" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="A6" s="32"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
       <c r="D6" s="13" t="s">
         <v>28</v>
       </c>
@@ -972,9 +972,9 @@
       <c r="R6" s="17"/>
     </row>
     <row r="7" spans="1:19" s="3" customFormat="1" ht="36" customHeight="1">
-      <c r="A7" s="32"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="33"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="34"/>
       <c r="D7" s="13" t="s">
         <v>30</v>
       </c>
@@ -999,8 +999,8 @@
       <c r="R7" s="17"/>
     </row>
     <row r="8" spans="1:19" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="33"/>
+      <c r="A8" s="34"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="12" t="s">
         <v>37</v>
       </c>
@@ -1151,7 +1151,7 @@
     <col min="2" max="2" width="11.83203125" style="3" customWidth="1"/>
     <col min="3" max="3" width="24.33203125" style="4" customWidth="1"/>
     <col min="4" max="4" width="13" style="5" customWidth="1"/>
-    <col min="5" max="5" width="10.1640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" style="3" customWidth="1"/>
     <col min="6" max="16" width="9.1640625" style="3"/>
     <col min="17" max="17" width="9.1640625" style="3" hidden="1" customWidth="1"/>
     <col min="18" max="19" width="9.1640625" style="3"/>
@@ -1165,24 +1165,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" s="1" customFormat="1" ht="45" customHeight="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
       <c r="W1" s="18"/>
     </row>
     <row r="2" spans="1:23" s="2" customFormat="1" ht="53" customHeight="1">
@@ -1248,10 +1248,10 @@
       </c>
     </row>
     <row r="3" spans="1:23" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="A3" s="31">
+      <c r="A3" s="32">
         <v>1</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="35" t="s">
         <v>44</v>
       </c>
       <c r="C3" s="13" t="s">
@@ -1260,25 +1260,27 @@
       <c r="D3" s="14">
         <v>5500</v>
       </c>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36"/>
-      <c r="P3" s="36"/>
+      <c r="E3" s="15">
+        <v>5500</v>
+      </c>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
       <c r="Q3" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="T3" s="31">
+      <c r="T3" s="32">
         <v>1</v>
       </c>
-      <c r="U3" s="34" t="s">
+      <c r="U3" s="35" t="s">
         <v>44</v>
       </c>
       <c r="V3" s="13" t="s">
@@ -1289,8 +1291,8 @@
       </c>
     </row>
     <row r="4" spans="1:23" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="A4" s="32"/>
-      <c r="B4" s="34"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="35"/>
       <c r="C4" s="13" t="s">
         <v>46</v>
       </c>
@@ -1298,20 +1300,23 @@
         <f>80+45+25+8</f>
         <v>158</v>
       </c>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="T4" s="32"/>
-      <c r="U4" s="34"/>
+      <c r="E4" s="15">
+        <f>60+100</f>
+        <v>160</v>
+      </c>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="35"/>
       <c r="V4" s="13" t="s">
         <v>46</v>
       </c>
@@ -1321,8 +1326,8 @@
       </c>
     </row>
     <row r="5" spans="1:23" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="A5" s="32"/>
-      <c r="B5" s="34"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="13" t="s">
         <v>47</v>
       </c>
@@ -1330,20 +1335,22 @@
         <f>1600+250</f>
         <v>1850</v>
       </c>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="T5" s="32"/>
-      <c r="U5" s="34"/>
+      <c r="E5" s="15">
+        <v>1656.3</v>
+      </c>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="T5" s="33"/>
+      <c r="U5" s="35"/>
       <c r="V5" s="13" t="s">
         <v>47</v>
       </c>
@@ -1353,28 +1360,31 @@
       </c>
     </row>
     <row r="6" spans="1:23" s="3" customFormat="1" ht="20" customHeight="1">
-      <c r="A6" s="32"/>
-      <c r="B6" s="34"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="13" t="s">
         <v>48</v>
       </c>
       <c r="D6" s="15">
         <v>1000</v>
       </c>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="T6" s="32"/>
-      <c r="U6" s="34"/>
+      <c r="E6" s="15">
+        <f>127.3+500</f>
+        <v>627.29999999999995</v>
+      </c>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="T6" s="33"/>
+      <c r="U6" s="35"/>
       <c r="V6" s="13" t="s">
         <v>48</v>
       </c>
@@ -1395,18 +1405,20 @@
       <c r="D7" s="14">
         <v>1000</v>
       </c>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
+      <c r="E7" s="15">
+        <v>0</v>
+      </c>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
       <c r="T7" s="16">
         <v>2</v>
       </c>
@@ -1424,15 +1436,18 @@
       <c r="A8" s="17">
         <v>3</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="34"/>
+      <c r="C8" s="35"/>
       <c r="D8" s="26">
         <f>SUM(D3:D7)</f>
         <v>9508</v>
       </c>
-      <c r="E8" s="17"/>
+      <c r="E8" s="26">
+        <f>SUM(E3:E7)</f>
+        <v>7943.6</v>
+      </c>
       <c r="F8" s="17"/>
       <c r="G8" s="17"/>
       <c r="H8" s="17"/>

--- a/苏老师22年计划表.xlsx
+++ b/苏老师22年计划表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kayla/Desktop/Workspace/kayla00822.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F778C63E-A33D-564F-9170-E4AB6772582A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F957E1E-A2B4-6C46-89B1-F89ADAE540AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="57">
   <si>
     <t>2022年1月计划跟进表</t>
   </si>
@@ -203,6 +203,10 @@
   </si>
   <si>
     <t>1月</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>week1</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1144,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:XFB8"/>
+  <dimension ref="A1:XFA11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.1640625" style="3"/>
@@ -1152,19 +1156,19 @@
     <col min="3" max="3" width="24.33203125" style="4" customWidth="1"/>
     <col min="4" max="4" width="13" style="5" customWidth="1"/>
     <col min="5" max="5" width="12.6640625" style="3" customWidth="1"/>
-    <col min="6" max="16" width="9.1640625" style="3"/>
-    <col min="17" max="17" width="9.1640625" style="3" hidden="1" customWidth="1"/>
-    <col min="18" max="19" width="9.1640625" style="3"/>
-    <col min="20" max="20" width="9.33203125" style="3" customWidth="1"/>
-    <col min="21" max="21" width="16.33203125" style="3" customWidth="1"/>
-    <col min="22" max="22" width="22.6640625" style="3" customWidth="1"/>
-    <col min="23" max="23" width="28.33203125" style="6" customWidth="1"/>
-    <col min="24" max="16362" width="9.1640625" style="3"/>
-    <col min="16363" max="16363" width="9.1640625" style="7"/>
-    <col min="16364" max="16382" width="9.1640625" style="8"/>
+    <col min="6" max="15" width="9.1640625" style="3"/>
+    <col min="16" max="16" width="9.1640625" style="3" hidden="1" customWidth="1"/>
+    <col min="17" max="18" width="9.1640625" style="3"/>
+    <col min="19" max="19" width="9.33203125" style="3" customWidth="1"/>
+    <col min="20" max="20" width="16.33203125" style="3" customWidth="1"/>
+    <col min="21" max="21" width="22.6640625" style="3" customWidth="1"/>
+    <col min="22" max="22" width="28.33203125" style="6" customWidth="1"/>
+    <col min="23" max="16361" width="9.1640625" style="3"/>
+    <col min="16362" max="16362" width="9.1640625" style="7"/>
+    <col min="16363" max="16381" width="9.1640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="1" customFormat="1" ht="45" customHeight="1">
+    <row r="1" spans="1:22" s="1" customFormat="1" ht="45" customHeight="1">
       <c r="A1" s="30" t="s">
         <v>39</v>
       </c>
@@ -1182,10 +1186,9 @@
       <c r="M1" s="30"/>
       <c r="N1" s="30"/>
       <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="W1" s="18"/>
-    </row>
-    <row r="2" spans="1:23" s="2" customFormat="1" ht="53" customHeight="1">
+      <c r="V1" s="18"/>
+    </row>
+    <row r="2" spans="1:22" s="2" customFormat="1" ht="53" customHeight="1">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -1202,52 +1205,49 @@
         <v>54</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P2" s="9" t="s">
         <v>18</v>
       </c>
+      <c r="S2" s="9" t="s">
+        <v>1</v>
+      </c>
       <c r="T2" s="9" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="U2" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="V2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="W2" s="19" t="s">
+      <c r="V2" s="19" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="3" customFormat="1" ht="20" customHeight="1">
+    <row r="3" spans="1:22" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A3" s="32">
         <v>1</v>
       </c>
@@ -1273,24 +1273,23 @@
       <c r="M3" s="29"/>
       <c r="N3" s="29"/>
       <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="17" t="s">
+      <c r="P3" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="T3" s="32">
+      <c r="S3" s="32">
         <v>1</v>
       </c>
-      <c r="U3" s="35" t="s">
+      <c r="T3" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="V3" s="13" t="s">
+      <c r="U3" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="W3" s="14">
+      <c r="V3" s="14">
         <v>5500</v>
       </c>
     </row>
-    <row r="4" spans="1:23" s="3" customFormat="1" ht="20" customHeight="1">
+    <row r="4" spans="1:22" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A4" s="33"/>
       <c r="B4" s="35"/>
       <c r="C4" s="13" t="s">
@@ -1314,18 +1313,17 @@
       <c r="M4" s="29"/>
       <c r="N4" s="29"/>
       <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="35"/>
-      <c r="V4" s="13" t="s">
+      <c r="S4" s="33"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="W4" s="14">
+      <c r="V4" s="14">
         <f>80+45+25+8</f>
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="3" customFormat="1" ht="20" customHeight="1">
+    <row r="5" spans="1:22" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A5" s="33"/>
       <c r="B5" s="35"/>
       <c r="C5" s="13" t="s">
@@ -1348,18 +1346,17 @@
       <c r="M5" s="29"/>
       <c r="N5" s="29"/>
       <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="T5" s="33"/>
-      <c r="U5" s="35"/>
-      <c r="V5" s="13" t="s">
+      <c r="S5" s="33"/>
+      <c r="T5" s="35"/>
+      <c r="U5" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="W5" s="14">
+      <c r="V5" s="14">
         <f>1600+250</f>
         <v>1850</v>
       </c>
     </row>
-    <row r="6" spans="1:23" s="3" customFormat="1" ht="20" customHeight="1">
+    <row r="6" spans="1:22" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A6" s="33"/>
       <c r="B6" s="35"/>
       <c r="C6" s="13" t="s">
@@ -1382,17 +1379,16 @@
       <c r="M6" s="29"/>
       <c r="N6" s="29"/>
       <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="T6" s="33"/>
-      <c r="U6" s="35"/>
-      <c r="V6" s="13" t="s">
+      <c r="S6" s="33"/>
+      <c r="T6" s="35"/>
+      <c r="U6" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="W6" s="15">
+      <c r="V6" s="15">
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="3" customFormat="1" ht="20" customHeight="1">
+    <row r="7" spans="1:22" s="3" customFormat="1" ht="20" customHeight="1">
       <c r="A7" s="16">
         <v>2</v>
       </c>
@@ -1418,21 +1414,20 @@
       <c r="M7" s="29"/>
       <c r="N7" s="29"/>
       <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="T7" s="16">
+      <c r="S7" s="16">
         <v>2</v>
       </c>
-      <c r="U7" s="16" t="s">
+      <c r="T7" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="V7" s="13" t="s">
+      <c r="U7" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="W7" s="14">
+      <c r="V7" s="14">
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="20" customHeight="1">
+    <row r="8" spans="1:22" ht="20" customHeight="1">
       <c r="A8" s="17">
         <v>3</v>
       </c>
@@ -1458,14 +1453,24 @@
       <c r="M8" s="17"/>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
+    </row>
+    <row r="10" spans="1:22" ht="20" customHeight="1">
+      <c r="F10" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="20" customHeight="1">
+      <c r="F11" s="3">
+        <f>50000-46465.7</f>
+        <v>3534.3000000000029</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="S3:S6"/>
     <mergeCell ref="T3:T6"/>
-    <mergeCell ref="U3:U6"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:O1"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="B3:B6"/>
   </mergeCells>
